--- a/ai4sh/import_data/utility/observation/excel/provision_indicator.xlsx
+++ b/ai4sh/import_data/utility/observation/excel/provision_indicator.xlsx
@@ -490,7 +490,7 @@
     <t xml:space="preserve">ai4sh-ibec</t>
   </si>
   <si>
-    <t xml:space="preserve">usda_ec</t>
+    <t xml:space="preserve">usda ec</t>
   </si>
   <si>
     <t xml:space="preserve">μS*cm^-1</t>
@@ -603,23 +603,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/ai4sh/import_data/utility/observation/excel/provision_indicator.xlsx
+++ b/ai4sh/import_data/utility/observation/excel/provision_indicator.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="167">
   <si>
     <t xml:space="preserve">provision_id__provision_name</t>
   </si>
@@ -503,6 +503,24 @@
   </si>
   <si>
     <t xml:space="preserve">Weight percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture iuss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">derived</t>
+  </si>
+  <si>
+    <t xml:space="preserve">class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture usda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture usda major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture iuss major group</t>
   </si>
 </sst>
 </file>
@@ -598,7 +616,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -620,6 +638,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2341,6 +2367,174 @@
         <v>160</v>
       </c>
     </row>
+    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
     <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
